--- a/data/generated/grille_1005_2026.xlsx
+++ b/data/generated/grille_1005_2026.xlsx
@@ -1075,7 +1075,7 @@
       <c r="B6" s="64" t="n"/>
       <c r="C6" s="65" t="inlineStr">
         <is>
-          <t>2026-04-20 — 2 voie mazas 75012 paris</t>
+          <t>2026-04-22 — Paris 12</t>
         </is>
       </c>
       <c r="D6" s="66" t="n"/>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>1800</v>
+        <v>14000</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>faible</t>
+          <t>moyen</t>
         </is>
       </c>
       <c r="D9" s="7">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>faible</t>
+          <t>moyen</t>
         </is>
       </c>
       <c r="D10" s="7">

--- a/data/generated/grille_1005_2026.xlsx
+++ b/data/generated/grille_1005_2026.xlsx
@@ -1073,11 +1073,7 @@
         </is>
       </c>
       <c r="B6" s="64" t="n"/>
-      <c r="C6" s="65" t="inlineStr">
-        <is>
-          <t>2026-04-22 — Paris 12</t>
-        </is>
-      </c>
+      <c r="C6" s="65" t="inlineStr"/>
       <c r="D6" s="66" t="n"/>
       <c r="E6" s="64" t="n"/>
       <c r="F6" s="1" t="n"/>
@@ -1142,7 +1138,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
@@ -1189,7 +1185,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>moyen</t>
+          <t>faible</t>
         </is>
       </c>
       <c r="D9" s="7">
@@ -1235,7 +1231,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>moyen</t>
+          <t>faible</t>
         </is>
       </c>
       <c r="D10" s="7">
